--- a/30_table/01_테스트버전/Table_List_DailyReward.xlsx
+++ b/30_table/01_테스트버전/Table_List_DailyReward.xlsx
@@ -3780,7 +3780,7 @@
         <v>42</v>
       </c>
       <c r="F2" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3801,7 +3801,7 @@
         <v>85</v>
       </c>
       <c r="F3" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3822,7 +3822,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3843,7 +3843,7 @@
         <v>85</v>
       </c>
       <c r="F5" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3864,7 +3864,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="34">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3885,7 +3885,7 @@
         <v>85</v>
       </c>
       <c r="F7" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3906,7 +3906,7 @@
         <v>86</v>
       </c>
       <c r="F8" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3927,7 +3927,7 @@
         <v>85</v>
       </c>
       <c r="F9" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3948,7 +3948,7 @@
         <v>86</v>
       </c>
       <c r="F10" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3990,7 +3990,7 @@
         <v>86</v>
       </c>
       <c r="F12" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -4011,7 +4011,7 @@
         <v>85</v>
       </c>
       <c r="F13" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -4032,7 +4032,7 @@
         <v>86</v>
       </c>
       <c r="F14" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -4053,7 +4053,7 @@
         <v>85</v>
       </c>
       <c r="F15" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -4074,7 +4074,7 @@
         <v>86</v>
       </c>
       <c r="F16" s="34">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -4095,7 +4095,7 @@
         <v>85</v>
       </c>
       <c r="F17" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -4116,7 +4116,7 @@
         <v>86</v>
       </c>
       <c r="F18" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -4137,7 +4137,7 @@
         <v>85</v>
       </c>
       <c r="F19" s="34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -4158,7 +4158,7 @@
         <v>86</v>
       </c>
       <c r="F20" s="34">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
